--- a/metalman-auto-engineer/backend/outputs/BOM_Result_92187158.xlsx
+++ b/metalman-auto-engineer/backend/outputs/BOM_Result_92187158.xlsx
@@ -2171,7 +2171,7 @@
         <is>
           <t xml:space="preserve">Format No - F/NPD/05
 Rev No : 00
-Rev Date: 24/04/2026 </t>
+Rev Date: 27/05/2026 </t>
         </is>
       </c>
       <c r="K1" s="58" t="n"/>

--- a/metalman-auto-engineer/backend/outputs/BOM_Result_92187158.xlsx
+++ b/metalman-auto-engineer/backend/outputs/BOM_Result_92187158.xlsx
@@ -1470,7 +1470,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1333500" cy="952500"/>
+    <ext cx="1524000" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -1495,7 +1495,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1333500" cy="952500"/>
+    <ext cx="1524000" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -1520,7 +1520,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1333500" cy="952500"/>
+    <ext cx="1524000" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -1545,7 +1545,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1333500" cy="952500"/>
+    <ext cx="1524000" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -1570,7 +1570,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1333500" cy="952500"/>
+    <ext cx="1524000" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -1595,7 +1595,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1333500" cy="952500"/>
+    <ext cx="1524000" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -1620,7 +1620,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1333500" cy="952500"/>
+    <ext cx="1524000" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -1645,7 +1645,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1333500" cy="952500"/>
+    <ext cx="1524000" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -1670,7 +1670,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1333500" cy="952500"/>
+    <ext cx="1524000" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1695,7 +1695,7 @@
       <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1333500" cy="952500"/>
+    <ext cx="1524000" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -1720,7 +1720,7 @@
       <row>15</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1333500" cy="952500"/>
+    <ext cx="1524000" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -1745,7 +1745,7 @@
       <row>16</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1333500" cy="952500"/>
+    <ext cx="1524000" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -1770,7 +1770,7 @@
       <row>17</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1333500" cy="952500"/>
+    <ext cx="1524000" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -1795,7 +1795,7 @@
       <row>19</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1333500" cy="952500"/>
+    <ext cx="1524000" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="15" name="Image 15" descr="Picture"/>
@@ -1820,7 +1820,7 @@
       <row>20</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1333500" cy="952500"/>
+    <ext cx="1524000" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="16" name="Image 16" descr="Picture"/>
@@ -1845,7 +1845,7 @@
       <row>21</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1333500" cy="952500"/>
+    <ext cx="1524000" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="17" name="Image 17" descr="Picture"/>
@@ -2142,7 +2142,7 @@
     <col width="12.08984375" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="13.36328125" customWidth="1" min="4" max="4"/>
     <col width="28.90625" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
     <col width="10.08984375" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
     <col width="14.08984375" customWidth="1" min="9" max="9"/>
@@ -2171,7 +2171,7 @@
         <is>
           <t xml:space="preserve">Format No - F/NPD/05
 Rev No : 00
-Rev Date: 27/05/2026 </t>
+Rev Date: 01/06/2026 </t>
         </is>
       </c>
       <c r="K1" s="58" t="n"/>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="80" customFormat="1" customHeight="1" s="5">
+    <row r="6" ht="105" customFormat="1" customHeight="1" s="5">
       <c r="A6" s="28" t="n">
         <v>1</v>
       </c>
@@ -2331,7 +2331,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="80" customFormat="1" customHeight="1" s="5">
+    <row r="7" ht="105" customFormat="1" customHeight="1" s="5">
       <c r="A7" s="28" t="n">
         <v>2</v>
       </c>
@@ -2383,7 +2383,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="80" customFormat="1" customHeight="1" s="5">
+    <row r="8" ht="105" customFormat="1" customHeight="1" s="5">
       <c r="A8" s="28" t="n">
         <v>3</v>
       </c>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="80" customFormat="1" customHeight="1" s="5">
+    <row r="9" ht="105" customFormat="1" customHeight="1" s="5">
       <c r="A9" s="28" t="n">
         <v>4</v>
       </c>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="80" customFormat="1" customHeight="1" s="5">
+    <row r="10" ht="105" customFormat="1" customHeight="1" s="5">
       <c r="A10" s="28" t="n">
         <v>5</v>
       </c>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="M10" s="8" t="n"/>
     </row>
-    <row r="11" ht="80" customFormat="1" customHeight="1" s="5">
+    <row r="11" ht="105" customFormat="1" customHeight="1" s="5">
       <c r="A11" s="28" t="n">
         <v>6</v>
       </c>
@@ -2592,7 +2592,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="80" customFormat="1" customHeight="1" s="5">
+    <row r="12" ht="105" customFormat="1" customHeight="1" s="5">
       <c r="A12" s="28" t="n">
         <v>7</v>
       </c>
@@ -2642,7 +2642,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="80" customFormat="1" customHeight="1" s="5">
+    <row r="13" ht="105" customFormat="1" customHeight="1" s="5">
       <c r="A13" s="28" t="n">
         <v>8</v>
       </c>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="M13" s="8" t="n"/>
     </row>
-    <row r="14" ht="80" customFormat="1" customHeight="1" s="5">
+    <row r="14" ht="105" customFormat="1" customHeight="1" s="5">
       <c r="A14" s="28" t="n">
         <v>9</v>
       </c>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="80" customFormat="1" customHeight="1" s="5">
+    <row r="15" ht="105" customFormat="1" customHeight="1" s="5">
       <c r="A15" s="28" t="n">
         <v>10</v>
       </c>
@@ -2799,7 +2799,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="80" customFormat="1" customHeight="1" s="5">
+    <row r="16" ht="105" customFormat="1" customHeight="1" s="5">
       <c r="A16" s="28" t="n">
         <v>11</v>
       </c>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="80" customFormat="1" customHeight="1" s="5">
+    <row r="17" ht="105" customFormat="1" customHeight="1" s="5">
       <c r="A17" s="28" t="n">
         <v>12</v>
       </c>
@@ -2899,7 +2899,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="80" customFormat="1" customHeight="1" s="5">
+    <row r="18" ht="105" customFormat="1" customHeight="1" s="5">
       <c r="A18" s="28" t="n">
         <v>13</v>
       </c>
@@ -2999,7 +2999,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="80" customFormat="1" customHeight="1" s="5">
+    <row r="20" ht="105" customFormat="1" customHeight="1" s="5">
       <c r="A20" s="28" t="n">
         <v>16</v>
       </c>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="80" customFormat="1" customHeight="1" s="5">
+    <row r="21" ht="105" customFormat="1" customHeight="1" s="5">
       <c r="A21" s="28" t="n">
         <v>17</v>
       </c>
@@ -3095,7 +3095,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="80" customFormat="1" customHeight="1" s="5" thickBot="1">
+    <row r="22" ht="105" customFormat="1" customHeight="1" s="5" thickBot="1">
       <c r="A22" s="31" t="n">
         <v>18</v>
       </c>

--- a/metalman-auto-engineer/backend/outputs/BOM_Result_92187158.xlsx
+++ b/metalman-auto-engineer/backend/outputs/BOM_Result_92187158.xlsx
@@ -2171,7 +2171,7 @@
         <is>
           <t xml:space="preserve">Format No - F/NPD/05
 Rev No : 00
-Rev Date: 01/06/2026 </t>
+Rev Date: 11/06/2026 </t>
         </is>
       </c>
       <c r="K1" s="58" t="n"/>
